--- a/excel/08逻辑判断IF函数.xlsx
+++ b/excel/08逻辑判断IF函数.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10914"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zimu/Desktop/cli/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zimu/Documents/data-analytics/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A06BBA3C-81C1-EA46-B232-08F4CF674EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B7B5C86-3E20-6941-86B0-38F9665321F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="124">
   <si>
     <t>二、</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -754,10 +754,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>IF(logical_test,[value_if_true],[value_if_false])</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>AND(logical_test1,logical_test2)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -770,18 +766,34 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>iserror(value*)</t>
+    <t>返回falsy值</t>
+  </si>
+  <si>
+    <t>计算错误返回指定值</t>
+  </si>
+  <si>
+    <t>IF(logical_test, value_if_true, [value_if_false])</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>返回falsy值</t>
-  </si>
-  <si>
-    <t>iferror(value*,value_if_error*)</t>
+    <t>IF函数前两个参数的必填参数 第三参数可选参数 参数三默认不填返回false</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>计算错误返回指定值</t>
+    <t>3、IFS函数相当于switchcase函数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ISERROR(value*)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IFERROR(value*,value_if_error*)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IFS([Something is True1, Value if True1,Something is True2,Value if True2,Something is True3,Value if True3)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -789,11 +801,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="177" formatCode="yy/m/d"/>
-    <numFmt numFmtId="178" formatCode="##\-###"/>
-    <numFmt numFmtId="179" formatCode="0.0_ "/>
+    <numFmt numFmtId="176" formatCode="yy/m/d"/>
+    <numFmt numFmtId="177" formatCode="##\-###"/>
+    <numFmt numFmtId="178" formatCode="0.0_ "/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -870,6 +882,13 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -926,7 +945,7 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
@@ -953,7 +972,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -969,18 +988,18 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="177" fontId="10" fillId="2" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="10" fillId="2" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -992,10 +1011,13 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -1307,7 +1329,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor indexed="60"/>
   </sheetPr>
-  <dimension ref="A2:G26"/>
+  <dimension ref="A2:G30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1335,96 +1357,119 @@
     </row>
     <row r="7" spans="1:6" s="3" customFormat="1" ht="14">
       <c r="B7" s="5"/>
-      <c r="C7" s="26" t="s">
-        <v>113</v>
+      <c r="C7" s="25" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:6" s="3" customFormat="1" ht="14">
       <c r="B8" s="5"/>
+      <c r="C8" s="27" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="9" spans="1:6" s="3" customFormat="1" ht="14">
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5"/>
+    </row>
+    <row r="10" spans="1:6" s="3" customFormat="1" ht="14">
+      <c r="B10" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" s="3" customFormat="1" ht="14">
+      <c r="C11" s="25" t="s">
+        <v>121</v>
+      </c>
+      <c r="F11" s="25" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="3" customFormat="1" ht="14">
-      <c r="C10" s="26" t="s">
+    <row r="12" spans="1:6" s="3" customFormat="1" ht="14">
+      <c r="C12" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="F12" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="F10" s="26" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" s="3" customFormat="1" ht="14">
-      <c r="C11" s="26" t="s">
-        <v>119</v>
-      </c>
-      <c r="F11" s="26" t="s">
+    </row>
+    <row r="13" spans="1:6" s="3" customFormat="1" ht="14">
+      <c r="C13" s="25"/>
+      <c r="F13" s="25"/>
+    </row>
+    <row r="14" spans="1:6" s="3" customFormat="1" ht="14">
+      <c r="B14" s="3" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" s="3" customFormat="1" ht="14"/>
-    <row r="13" spans="1:6" s="3" customFormat="1" ht="14">
-      <c r="A13" s="3" t="s">
+      <c r="C14" s="25"/>
+      <c r="F14" s="25"/>
+    </row>
+    <row r="15" spans="1:6" s="3" customFormat="1" ht="14">
+      <c r="C15" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="F15" s="25"/>
+    </row>
+    <row r="16" spans="1:6" s="3" customFormat="1" ht="14"/>
+    <row r="17" spans="1:7" s="3" customFormat="1" ht="14">
+      <c r="A17" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B17" s="7" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="14" spans="1:6" s="3" customFormat="1" ht="14"/>
-    <row r="15" spans="1:6" s="3" customFormat="1" ht="14">
-      <c r="B15" s="5" t="s">
+    <row r="18" spans="1:7" s="3" customFormat="1" ht="14"/>
+    <row r="19" spans="1:7" s="3" customFormat="1" ht="14">
+      <c r="B19" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="16" spans="1:6" s="3" customFormat="1" ht="14">
-      <c r="B16" s="5"/>
-      <c r="C16" s="26" t="s">
+    <row r="20" spans="1:7" s="3" customFormat="1" ht="14">
+      <c r="B20" s="5"/>
+      <c r="C20" s="25" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" s="3" customFormat="1" ht="14">
+      <c r="C21" s="4"/>
+    </row>
+    <row r="22" spans="1:7" s="3" customFormat="1">
+      <c r="B22" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C22" s="5"/>
+      <c r="G22" s="6"/>
+    </row>
+    <row r="23" spans="1:7" s="3" customFormat="1" ht="14">
+      <c r="C23" s="25" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="17" spans="2:7" s="3" customFormat="1" ht="14">
-      <c r="C17" s="4"/>
-    </row>
-    <row r="18" spans="2:7" s="3" customFormat="1">
-      <c r="B18" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C18" s="5"/>
-      <c r="G18" s="6"/>
-    </row>
-    <row r="19" spans="2:7" s="3" customFormat="1" ht="14">
-      <c r="C19" s="26" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" s="3" customFormat="1" ht="14"/>
-    <row r="21" spans="2:7">
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="E21" s="3"/>
-    </row>
-    <row r="22" spans="2:7">
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="E22" s="3"/>
-    </row>
-    <row r="23" spans="2:7">
-      <c r="B23" s="3"/>
-      <c r="E23" s="3"/>
-    </row>
-    <row r="24" spans="2:7">
-      <c r="B24" s="3"/>
-      <c r="E24" s="3"/>
-    </row>
-    <row r="25" spans="2:7">
+    <row r="24" spans="1:7" s="3" customFormat="1" ht="14"/>
+    <row r="25" spans="1:7">
       <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
       <c r="E25" s="3"/>
     </row>
-    <row r="26" spans="2:7">
+    <row r="26" spans="1:7">
       <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
       <c r="E26" s="3"/>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="B27" s="3"/>
+      <c r="E27" s="3"/>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="B28" s="3"/>
+      <c r="E28" s="3"/>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="B29" s="3"/>
+      <c r="E29" s="3"/>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="B30" s="3"/>
+      <c r="E30" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2532,13 +2577,13 @@
         <v>第二批</v>
       </c>
       <c r="M8" s="13"/>
-      <c r="N8" s="25" t="s">
+      <c r="N8" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="O8" s="25"/>
-      <c r="P8" s="25"/>
-      <c r="Q8" s="25"/>
-      <c r="R8" s="25"/>
+      <c r="O8" s="26"/>
+      <c r="P8" s="26"/>
+      <c r="Q8" s="26"/>
+      <c r="R8" s="26"/>
       <c r="S8" s="15"/>
     </row>
     <row r="9" spans="1:19" ht="15">
@@ -2577,13 +2622,13 @@
         <v>第一批</v>
       </c>
       <c r="M9" s="13"/>
-      <c r="N9" s="25" t="s">
+      <c r="N9" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="O9" s="25"/>
-      <c r="P9" s="25"/>
-      <c r="Q9" s="25"/>
-      <c r="R9" s="25"/>
+      <c r="O9" s="26"/>
+      <c r="P9" s="26"/>
+      <c r="Q9" s="26"/>
+      <c r="R9" s="26"/>
       <c r="S9" s="15"/>
     </row>
     <row r="10" spans="1:19" ht="15">
@@ -2622,13 +2667,13 @@
         <v>第一批</v>
       </c>
       <c r="M10" s="13"/>
-      <c r="N10" s="25" t="s">
+      <c r="N10" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="O10" s="25"/>
-      <c r="P10" s="25"/>
-      <c r="Q10" s="25"/>
-      <c r="R10" s="25"/>
+      <c r="O10" s="26"/>
+      <c r="P10" s="26"/>
+      <c r="Q10" s="26"/>
+      <c r="R10" s="26"/>
       <c r="S10" s="15"/>
     </row>
     <row r="11" spans="1:19" ht="15">

--- a/excel/08逻辑判断IF函数.xlsx
+++ b/excel/08逻辑判断IF函数.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10914"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10927"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zimu/Documents/data-analytics/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B7B5C86-3E20-6941-86B0-38F9665321F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{593716D8-1A90-0545-9C48-7FC027C1B4DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="126">
   <si>
     <t>二、</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -793,6 +793,14 @@
   </si>
   <si>
     <t>IFS([Something is True1, Value if True1,Something is True2,Value if True2,Something is True3,Value if True3)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3、NOT函数：表示“非”的关系</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NOT(logical_test)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1014,11 +1022,11 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1363,7 +1371,7 @@
     </row>
     <row r="8" spans="1:6" s="3" customFormat="1" ht="14">
       <c r="B8" s="5"/>
-      <c r="C8" s="27" t="s">
+      <c r="C8" s="26" t="s">
         <v>119</v>
       </c>
     </row>
@@ -1446,13 +1454,17 @@
     </row>
     <row r="24" spans="1:7" s="3" customFormat="1" ht="14"/>
     <row r="25" spans="1:7">
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
+      <c r="B25" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C25" s="5"/>
       <c r="E25" s="3"/>
     </row>
     <row r="26" spans="1:7">
       <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
+      <c r="C26" s="25" t="s">
+        <v>125</v>
+      </c>
       <c r="E26" s="3"/>
     </row>
     <row r="27" spans="1:7">
@@ -2577,13 +2589,13 @@
         <v>第二批</v>
       </c>
       <c r="M8" s="13"/>
-      <c r="N8" s="26" t="s">
+      <c r="N8" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="O8" s="26"/>
-      <c r="P8" s="26"/>
-      <c r="Q8" s="26"/>
-      <c r="R8" s="26"/>
+      <c r="O8" s="27"/>
+      <c r="P8" s="27"/>
+      <c r="Q8" s="27"/>
+      <c r="R8" s="27"/>
       <c r="S8" s="15"/>
     </row>
     <row r="9" spans="1:19" ht="15">
@@ -2622,13 +2634,13 @@
         <v>第一批</v>
       </c>
       <c r="M9" s="13"/>
-      <c r="N9" s="26" t="s">
+      <c r="N9" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="O9" s="26"/>
-      <c r="P9" s="26"/>
-      <c r="Q9" s="26"/>
-      <c r="R9" s="26"/>
+      <c r="O9" s="27"/>
+      <c r="P9" s="27"/>
+      <c r="Q9" s="27"/>
+      <c r="R9" s="27"/>
       <c r="S9" s="15"/>
     </row>
     <row r="10" spans="1:19" ht="15">
@@ -2667,13 +2679,13 @@
         <v>第一批</v>
       </c>
       <c r="M10" s="13"/>
-      <c r="N10" s="26" t="s">
+      <c r="N10" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="O10" s="26"/>
-      <c r="P10" s="26"/>
-      <c r="Q10" s="26"/>
-      <c r="R10" s="26"/>
+      <c r="O10" s="27"/>
+      <c r="P10" s="27"/>
+      <c r="Q10" s="27"/>
+      <c r="R10" s="27"/>
       <c r="S10" s="15"/>
     </row>
     <row r="11" spans="1:19" ht="15">
